--- a/hospital/стены/hospital-walls.xlsx
+++ b/hospital/стены/hospital-walls.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="черновик 1-5" sheetId="16" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="835">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -2534,6 +2534,10 @@
   </si>
   <si>
     <t>пог.м</t>
+  </si>
+  <si>
+    <t>2, 3 этаж
+базовая шпаклевка</t>
   </si>
 </sst>
 </file>
@@ -2995,7 +2999,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3175,6 +3179,96 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3187,116 +3281,35 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3627,186 +3640,186 @@
       <c r="G1" s="77"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="78" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82" t="s">
+      <c r="C2" s="79"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="67" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84">
+      <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="81" t="s">
         <v>516</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="88" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="69" t="s">
         <v>830</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="89">
+      <c r="G3" s="70">
         <f>C12</f>
         <v>4102.8599999999997</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="85" t="s">
         <v>818</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="68" t="s">
         <v>819</v>
       </c>
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="68" t="s">
         <v>820</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="68" t="s">
         <v>822</v>
       </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="84">
+      <c r="A7" s="68">
         <v>1</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="68" t="s">
         <v>823</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="71">
         <f>D7*3.8</f>
         <v>866.4</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="71">
         <v>228</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="84">
+      <c r="A8" s="68">
         <v>2</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="72" t="s">
         <v>824</v>
       </c>
-      <c r="C8" s="93">
+      <c r="C8" s="71">
         <f>D8*3.8</f>
         <v>938.9799999999999</v>
       </c>
-      <c r="D8" s="93">
+      <c r="D8" s="71">
         <v>247.1</v>
       </c>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="84">
+      <c r="A9" s="68">
         <v>3</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="68" t="s">
         <v>825</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="71">
         <f>D9*3.8</f>
         <v>925.68</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="71">
         <v>243.6</v>
       </c>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="84">
+      <c r="A10" s="68">
         <v>4</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="68" t="s">
         <v>826</v>
       </c>
-      <c r="C10" s="93">
+      <c r="C10" s="71">
         <f>D10*3.8</f>
         <v>925.68</v>
       </c>
-      <c r="D10" s="93">
+      <c r="D10" s="71">
         <v>243.6</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="84">
+      <c r="A11" s="68">
         <v>5</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="68" t="s">
         <v>827</v>
       </c>
-      <c r="C11" s="93">
+      <c r="C11" s="71">
         <f>D11*3.8</f>
         <v>446.12</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="71">
         <v>117.4</v>
       </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="87" t="s">
         <v>828</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="97">
+      <c r="B12" s="88"/>
+      <c r="C12" s="73">
         <f>SUM(C7:C11)</f>
         <v>4102.8599999999997</v>
       </c>
-      <c r="D12" s="97">
+      <c r="D12" s="73">
         <v>1200</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
     </row>
     <row r="17" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
@@ -3970,7 +3983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -4030,7 +4043,7 @@
         <v>100.98</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="90" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A5" s="42">
         <v>4</v>
       </c>
@@ -4193,7 +4206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -4253,7 +4266,7 @@
         <v>138.798</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="90" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A5" s="42">
         <v>4</v>
       </c>
@@ -4641,61 +4654,61 @@
       <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
     </row>
     <row r="5" spans="1:18" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
@@ -4748,17 +4761,17 @@
       <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
@@ -4774,15 +4787,15 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -4798,15 +4811,15 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -4822,15 +4835,15 @@
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -4846,15 +4859,15 @@
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -4870,15 +4883,15 @@
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -4894,15 +4907,15 @@
       <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -7940,15 +7953,15 @@
       <c r="B108" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="69" t="s">
+      <c r="C108" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="D108" s="70"/>
-      <c r="E108" s="70"/>
-      <c r="F108" s="70"/>
-      <c r="G108" s="70"/>
-      <c r="H108" s="70"/>
-      <c r="I108" s="70"/>
+      <c r="D108" s="94"/>
+      <c r="E108" s="94"/>
+      <c r="F108" s="94"/>
+      <c r="G108" s="94"/>
+      <c r="H108" s="94"/>
+      <c r="I108" s="94"/>
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -7964,15 +7977,15 @@
       <c r="B109" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C109" s="69" t="s">
+      <c r="C109" s="93" t="s">
         <v>169</v>
       </c>
-      <c r="D109" s="70"/>
-      <c r="E109" s="70"/>
-      <c r="F109" s="70"/>
-      <c r="G109" s="70"/>
-      <c r="H109" s="70"/>
-      <c r="I109" s="70"/>
+      <c r="D109" s="94"/>
+      <c r="E109" s="94"/>
+      <c r="F109" s="94"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
+      <c r="I109" s="94"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -7988,15 +8001,15 @@
       <c r="B110" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="69" t="s">
+      <c r="C110" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="70"/>
-      <c r="E110" s="70"/>
-      <c r="F110" s="70"/>
-      <c r="G110" s="70"/>
-      <c r="H110" s="70"/>
-      <c r="I110" s="70"/>
+      <c r="D110" s="94"/>
+      <c r="E110" s="94"/>
+      <c r="F110" s="94"/>
+      <c r="G110" s="94"/>
+      <c r="H110" s="94"/>
+      <c r="I110" s="94"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
       <c r="L110" s="9"/>
@@ -8012,15 +8025,15 @@
       <c r="B111" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C111" s="69" t="s">
+      <c r="C111" s="93" t="s">
         <v>175</v>
       </c>
-      <c r="D111" s="70"/>
-      <c r="E111" s="70"/>
-      <c r="F111" s="70"/>
-      <c r="G111" s="70"/>
-      <c r="H111" s="70"/>
-      <c r="I111" s="70"/>
+      <c r="D111" s="94"/>
+      <c r="E111" s="94"/>
+      <c r="F111" s="94"/>
+      <c r="G111" s="94"/>
+      <c r="H111" s="94"/>
+      <c r="I111" s="94"/>
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
@@ -8036,15 +8049,15 @@
       <c r="B112" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C112" s="69" t="s">
+      <c r="C112" s="93" t="s">
         <v>178</v>
       </c>
-      <c r="D112" s="70"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="70"/>
-      <c r="H112" s="70"/>
-      <c r="I112" s="70"/>
+      <c r="D112" s="94"/>
+      <c r="E112" s="94"/>
+      <c r="F112" s="94"/>
+      <c r="G112" s="94"/>
+      <c r="H112" s="94"/>
+      <c r="I112" s="94"/>
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
       <c r="L112" s="9"/>
@@ -8771,15 +8784,15 @@
       <c r="B135" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C135" s="69" t="s">
+      <c r="C135" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="70"/>
-      <c r="E135" s="70"/>
-      <c r="F135" s="70"/>
-      <c r="G135" s="70"/>
-      <c r="H135" s="70"/>
-      <c r="I135" s="70"/>
+      <c r="D135" s="94"/>
+      <c r="E135" s="94"/>
+      <c r="F135" s="94"/>
+      <c r="G135" s="94"/>
+      <c r="H135" s="94"/>
+      <c r="I135" s="94"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -10306,15 +10319,15 @@
       <c r="B180" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C180" s="69" t="s">
+      <c r="C180" s="93" t="s">
         <v>285</v>
       </c>
-      <c r="D180" s="70"/>
-      <c r="E180" s="70"/>
-      <c r="F180" s="70"/>
-      <c r="G180" s="70"/>
-      <c r="H180" s="70"/>
-      <c r="I180" s="70"/>
+      <c r="D180" s="94"/>
+      <c r="E180" s="94"/>
+      <c r="F180" s="94"/>
+      <c r="G180" s="94"/>
+      <c r="H180" s="94"/>
+      <c r="I180" s="94"/>
       <c r="J180" s="9"/>
       <c r="K180" s="9"/>
       <c r="L180" s="9"/>
@@ -13667,15 +13680,15 @@
       <c r="B285" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C285" s="69" t="s">
+      <c r="C285" s="93" t="s">
         <v>433</v>
       </c>
-      <c r="D285" s="70"/>
-      <c r="E285" s="70"/>
-      <c r="F285" s="70"/>
-      <c r="G285" s="70"/>
-      <c r="H285" s="70"/>
-      <c r="I285" s="70"/>
+      <c r="D285" s="94"/>
+      <c r="E285" s="94"/>
+      <c r="F285" s="94"/>
+      <c r="G285" s="94"/>
+      <c r="H285" s="94"/>
+      <c r="I285" s="94"/>
       <c r="J285" s="9"/>
       <c r="K285" s="9"/>
       <c r="L285" s="9"/>
@@ -13691,15 +13704,15 @@
       <c r="B286" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C286" s="69" t="s">
+      <c r="C286" s="93" t="s">
         <v>436</v>
       </c>
-      <c r="D286" s="70"/>
-      <c r="E286" s="70"/>
-      <c r="F286" s="70"/>
-      <c r="G286" s="70"/>
-      <c r="H286" s="70"/>
-      <c r="I286" s="70"/>
+      <c r="D286" s="94"/>
+      <c r="E286" s="94"/>
+      <c r="F286" s="94"/>
+      <c r="G286" s="94"/>
+      <c r="H286" s="94"/>
+      <c r="I286" s="94"/>
       <c r="J286" s="9"/>
       <c r="K286" s="9"/>
       <c r="L286" s="9"/>
@@ -14036,15 +14049,15 @@
       <c r="B297" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C297" s="69" t="s">
+      <c r="C297" s="93" t="s">
         <v>455</v>
       </c>
-      <c r="D297" s="70"/>
-      <c r="E297" s="70"/>
-      <c r="F297" s="70"/>
-      <c r="G297" s="70"/>
-      <c r="H297" s="70"/>
-      <c r="I297" s="70"/>
+      <c r="D297" s="94"/>
+      <c r="E297" s="94"/>
+      <c r="F297" s="94"/>
+      <c r="G297" s="94"/>
+      <c r="H297" s="94"/>
+      <c r="I297" s="94"/>
       <c r="J297" s="9"/>
       <c r="K297" s="9"/>
       <c r="L297" s="9"/>
@@ -14914,15 +14927,15 @@
       <c r="B324" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C324" s="69" t="s">
+      <c r="C324" s="93" t="s">
         <v>498</v>
       </c>
-      <c r="D324" s="70"/>
-      <c r="E324" s="70"/>
-      <c r="F324" s="70"/>
-      <c r="G324" s="70"/>
-      <c r="H324" s="70"/>
-      <c r="I324" s="70"/>
+      <c r="D324" s="94"/>
+      <c r="E324" s="94"/>
+      <c r="F324" s="94"/>
+      <c r="G324" s="94"/>
+      <c r="H324" s="94"/>
+      <c r="I324" s="94"/>
       <c r="J324" s="9"/>
       <c r="K324" s="9"/>
       <c r="L324" s="9"/>
@@ -14938,15 +14951,15 @@
       <c r="B325" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C325" s="69" t="s">
+      <c r="C325" s="93" t="s">
         <v>501</v>
       </c>
-      <c r="D325" s="70"/>
-      <c r="E325" s="70"/>
-      <c r="F325" s="70"/>
-      <c r="G325" s="70"/>
-      <c r="H325" s="70"/>
-      <c r="I325" s="70"/>
+      <c r="D325" s="94"/>
+      <c r="E325" s="94"/>
+      <c r="F325" s="94"/>
+      <c r="G325" s="94"/>
+      <c r="H325" s="94"/>
+      <c r="I325" s="94"/>
       <c r="J325" s="9"/>
       <c r="K325" s="9"/>
       <c r="L325" s="9"/>
@@ -15476,15 +15489,15 @@
       <c r="B342" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C342" s="69" t="s">
+      <c r="C342" s="93" t="s">
         <v>525</v>
       </c>
-      <c r="D342" s="70"/>
-      <c r="E342" s="70"/>
-      <c r="F342" s="70"/>
-      <c r="G342" s="70"/>
-      <c r="H342" s="70"/>
-      <c r="I342" s="70"/>
+      <c r="D342" s="94"/>
+      <c r="E342" s="94"/>
+      <c r="F342" s="94"/>
+      <c r="G342" s="94"/>
+      <c r="H342" s="94"/>
+      <c r="I342" s="94"/>
       <c r="J342" s="9"/>
       <c r="K342" s="9"/>
       <c r="L342" s="9"/>
@@ -16296,15 +16309,15 @@
       <c r="B367" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C367" s="69" t="s">
+      <c r="C367" s="93" t="s">
         <v>559</v>
       </c>
-      <c r="D367" s="70"/>
-      <c r="E367" s="70"/>
-      <c r="F367" s="70"/>
-      <c r="G367" s="70"/>
-      <c r="H367" s="70"/>
-      <c r="I367" s="70"/>
+      <c r="D367" s="94"/>
+      <c r="E367" s="94"/>
+      <c r="F367" s="94"/>
+      <c r="G367" s="94"/>
+      <c r="H367" s="94"/>
+      <c r="I367" s="94"/>
       <c r="J367" s="9"/>
       <c r="K367" s="9"/>
       <c r="L367" s="9"/>
@@ -18808,15 +18821,15 @@
       <c r="B447" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C447" s="69" t="s">
+      <c r="C447" s="93" t="s">
         <v>664</v>
       </c>
-      <c r="D447" s="70"/>
-      <c r="E447" s="70"/>
-      <c r="F447" s="70"/>
-      <c r="G447" s="70"/>
-      <c r="H447" s="70"/>
-      <c r="I447" s="70"/>
+      <c r="D447" s="94"/>
+      <c r="E447" s="94"/>
+      <c r="F447" s="94"/>
+      <c r="G447" s="94"/>
+      <c r="H447" s="94"/>
+      <c r="I447" s="94"/>
       <c r="J447" s="9"/>
       <c r="K447" s="9"/>
       <c r="L447" s="9"/>
@@ -18904,17 +18917,17 @@
       <c r="P449" s="9"/>
     </row>
     <row r="450" spans="1:18" ht="64.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A450" s="73" t="s">
+      <c r="A450" s="91" t="s">
         <v>671</v>
       </c>
-      <c r="B450" s="74"/>
-      <c r="C450" s="74"/>
-      <c r="D450" s="74"/>
-      <c r="E450" s="74"/>
-      <c r="F450" s="74"/>
-      <c r="G450" s="74"/>
-      <c r="H450" s="74"/>
-      <c r="I450" s="74"/>
+      <c r="B450" s="92"/>
+      <c r="C450" s="92"/>
+      <c r="D450" s="92"/>
+      <c r="E450" s="92"/>
+      <c r="F450" s="92"/>
+      <c r="G450" s="92"/>
+      <c r="H450" s="92"/>
+      <c r="I450" s="92"/>
       <c r="J450" s="26"/>
       <c r="K450" s="26"/>
       <c r="L450" s="26"/>
@@ -18930,15 +18943,15 @@
       <c r="B451" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C451" s="69" t="s">
+      <c r="C451" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="70"/>
-      <c r="E451" s="70"/>
-      <c r="F451" s="70"/>
-      <c r="G451" s="70"/>
-      <c r="H451" s="70"/>
-      <c r="I451" s="70"/>
+      <c r="D451" s="94"/>
+      <c r="E451" s="94"/>
+      <c r="F451" s="94"/>
+      <c r="G451" s="94"/>
+      <c r="H451" s="94"/>
+      <c r="I451" s="94"/>
       <c r="J451" s="9"/>
       <c r="K451" s="9"/>
       <c r="L451" s="9"/>
@@ -18954,15 +18967,15 @@
       <c r="B452" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C452" s="69" t="s">
+      <c r="C452" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D452" s="70"/>
-      <c r="E452" s="70"/>
-      <c r="F452" s="70"/>
-      <c r="G452" s="70"/>
-      <c r="H452" s="70"/>
-      <c r="I452" s="70"/>
+      <c r="D452" s="94"/>
+      <c r="E452" s="94"/>
+      <c r="F452" s="94"/>
+      <c r="G452" s="94"/>
+      <c r="H452" s="94"/>
+      <c r="I452" s="94"/>
       <c r="J452" s="9"/>
       <c r="K452" s="9"/>
       <c r="L452" s="9"/>
@@ -18978,15 +18991,15 @@
       <c r="B453" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C453" s="69" t="s">
+      <c r="C453" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="D453" s="70"/>
-      <c r="E453" s="70"/>
-      <c r="F453" s="70"/>
-      <c r="G453" s="70"/>
-      <c r="H453" s="70"/>
-      <c r="I453" s="70"/>
+      <c r="D453" s="94"/>
+      <c r="E453" s="94"/>
+      <c r="F453" s="94"/>
+      <c r="G453" s="94"/>
+      <c r="H453" s="94"/>
+      <c r="I453" s="94"/>
       <c r="J453" s="9"/>
       <c r="K453" s="9"/>
       <c r="L453" s="9"/>
@@ -19002,15 +19015,15 @@
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C454" s="69" t="s">
+      <c r="C454" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="D454" s="70"/>
-      <c r="E454" s="70"/>
-      <c r="F454" s="70"/>
-      <c r="G454" s="70"/>
-      <c r="H454" s="70"/>
-      <c r="I454" s="70"/>
+      <c r="D454" s="94"/>
+      <c r="E454" s="94"/>
+      <c r="F454" s="94"/>
+      <c r="G454" s="94"/>
+      <c r="H454" s="94"/>
+      <c r="I454" s="94"/>
       <c r="J454" s="9"/>
       <c r="K454" s="9"/>
       <c r="L454" s="9"/>
@@ -19026,15 +19039,15 @@
       <c r="B455" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C455" s="69" t="s">
+      <c r="C455" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D455" s="70"/>
-      <c r="E455" s="70"/>
-      <c r="F455" s="70"/>
-      <c r="G455" s="70"/>
-      <c r="H455" s="70"/>
-      <c r="I455" s="70"/>
+      <c r="D455" s="94"/>
+      <c r="E455" s="94"/>
+      <c r="F455" s="94"/>
+      <c r="G455" s="94"/>
+      <c r="H455" s="94"/>
+      <c r="I455" s="94"/>
       <c r="J455" s="9"/>
       <c r="K455" s="9"/>
       <c r="L455" s="9"/>
@@ -19050,15 +19063,15 @@
       <c r="B456" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C456" s="71" t="s">
+      <c r="C456" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D456" s="72"/>
-      <c r="E456" s="72"/>
-      <c r="F456" s="72"/>
-      <c r="G456" s="72"/>
-      <c r="H456" s="72"/>
-      <c r="I456" s="72"/>
+      <c r="D456" s="100"/>
+      <c r="E456" s="100"/>
+      <c r="F456" s="100"/>
+      <c r="G456" s="100"/>
+      <c r="H456" s="100"/>
+      <c r="I456" s="100"/>
       <c r="J456" s="27"/>
       <c r="K456" s="27"/>
       <c r="L456" s="27"/>
@@ -20621,15 +20634,15 @@
       <c r="B505" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="C505" s="67" t="s">
+      <c r="C505" s="97" t="s">
         <v>433</v>
       </c>
-      <c r="D505" s="68"/>
-      <c r="E505" s="68"/>
-      <c r="F505" s="68"/>
-      <c r="G505" s="68"/>
-      <c r="H505" s="68"/>
-      <c r="I505" s="68"/>
+      <c r="D505" s="98"/>
+      <c r="E505" s="98"/>
+      <c r="F505" s="98"/>
+      <c r="G505" s="98"/>
+      <c r="H505" s="98"/>
+      <c r="I505" s="98"/>
       <c r="J505" s="9"/>
       <c r="K505" s="29"/>
       <c r="L505" s="9"/>
@@ -20645,15 +20658,15 @@
       <c r="B506" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="C506" s="67" t="s">
+      <c r="C506" s="97" t="s">
         <v>436</v>
       </c>
-      <c r="D506" s="68"/>
-      <c r="E506" s="68"/>
-      <c r="F506" s="68"/>
-      <c r="G506" s="68"/>
-      <c r="H506" s="68"/>
-      <c r="I506" s="68"/>
+      <c r="D506" s="98"/>
+      <c r="E506" s="98"/>
+      <c r="F506" s="98"/>
+      <c r="G506" s="98"/>
+      <c r="H506" s="98"/>
+      <c r="I506" s="98"/>
       <c r="J506" s="9"/>
       <c r="K506" s="29"/>
       <c r="L506" s="9"/>
@@ -20815,15 +20828,15 @@
       <c r="B512" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="C512" s="67" t="s">
+      <c r="C512" s="97" t="s">
         <v>455</v>
       </c>
-      <c r="D512" s="68"/>
-      <c r="E512" s="68"/>
-      <c r="F512" s="68"/>
-      <c r="G512" s="68"/>
-      <c r="H512" s="68"/>
-      <c r="I512" s="68"/>
+      <c r="D512" s="98"/>
+      <c r="E512" s="98"/>
+      <c r="F512" s="98"/>
+      <c r="G512" s="98"/>
+      <c r="H512" s="98"/>
+      <c r="I512" s="98"/>
       <c r="J512" s="9"/>
       <c r="K512" s="29"/>
       <c r="L512" s="9"/>
@@ -21012,7 +21025,7 @@
       <c r="O518" s="8"/>
       <c r="P518" s="9"/>
     </row>
-    <row r="519" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>742</v>
       </c>
@@ -21260,22 +21273,35 @@
       <c r="E528" s="54"/>
       <c r="F528" s="54"/>
       <c r="G528" s="54"/>
-      <c r="H528" s="65"/>
-      <c r="I528" s="66"/>
-      <c r="J528" s="66"/>
-      <c r="K528" s="66"/>
-      <c r="L528" s="66"/>
-      <c r="M528" s="66"/>
-      <c r="N528" s="66"/>
-      <c r="O528" s="66"/>
+      <c r="H528" s="95"/>
+      <c r="I528" s="96"/>
+      <c r="J528" s="96"/>
+      <c r="K528" s="96"/>
+      <c r="L528" s="96"/>
+      <c r="M528" s="96"/>
+      <c r="N528" s="96"/>
+      <c r="O528" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="H528:O528"/>
+    <mergeCell ref="C505:I505"/>
+    <mergeCell ref="C506:I506"/>
+    <mergeCell ref="C512:I512"/>
+    <mergeCell ref="C455:I455"/>
+    <mergeCell ref="C456:I456"/>
+    <mergeCell ref="C454:I454"/>
+    <mergeCell ref="C286:I286"/>
+    <mergeCell ref="C297:I297"/>
+    <mergeCell ref="C324:I324"/>
+    <mergeCell ref="C325:I325"/>
+    <mergeCell ref="C342:I342"/>
+    <mergeCell ref="C367:I367"/>
+    <mergeCell ref="C447:I447"/>
+    <mergeCell ref="A450:I450"/>
+    <mergeCell ref="C451:I451"/>
+    <mergeCell ref="C452:I452"/>
+    <mergeCell ref="C453:I453"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C285:I285"/>
     <mergeCell ref="C9:I9"/>
@@ -21289,24 +21315,11 @@
     <mergeCell ref="C112:I112"/>
     <mergeCell ref="C135:I135"/>
     <mergeCell ref="C180:I180"/>
-    <mergeCell ref="C454:I454"/>
-    <mergeCell ref="C286:I286"/>
-    <mergeCell ref="C297:I297"/>
-    <mergeCell ref="C324:I324"/>
-    <mergeCell ref="C325:I325"/>
-    <mergeCell ref="C342:I342"/>
-    <mergeCell ref="C367:I367"/>
-    <mergeCell ref="C447:I447"/>
-    <mergeCell ref="A450:I450"/>
-    <mergeCell ref="C451:I451"/>
-    <mergeCell ref="C452:I452"/>
-    <mergeCell ref="C453:I453"/>
-    <mergeCell ref="H528:O528"/>
-    <mergeCell ref="C505:I505"/>
-    <mergeCell ref="C506:I506"/>
-    <mergeCell ref="C512:I512"/>
-    <mergeCell ref="C455:I455"/>
-    <mergeCell ref="C456:I456"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C7:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21315,13 +21328,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
     <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5546875" customWidth="1"/>
@@ -21337,139 +21350,103 @@
       <c r="E1" s="77"/>
       <c r="F1" s="77"/>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+    <row r="2" spans="1:6" s="110" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="76" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="108" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="100" t="s">
+      <c r="C2" s="109"/>
+      <c r="D2" s="76" t="s">
         <v>758</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="67" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84">
+      <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="81" t="s">
         <v>832</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="101" t="s">
-        <v>830</v>
-      </c>
-      <c r="E3" s="84" t="s">
+      <c r="C3" s="83"/>
+      <c r="D3" s="75" t="s">
+        <v>834</v>
+      </c>
+      <c r="E3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="89">
-        <f>B11</f>
-        <v>3746.48</v>
+      <c r="F3" s="70">
+        <f>B8</f>
+        <v>1594.8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="68" t="s">
         <v>831</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="84">
-        <v>1</v>
-      </c>
-      <c r="B6" s="89">
-        <v>752.48</v>
-      </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
+      <c r="A6" s="68">
+        <v>2</v>
+      </c>
+      <c r="B6" s="70">
+        <v>806</v>
+      </c>
+      <c r="C6" s="101"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="84">
-        <v>2</v>
-      </c>
-      <c r="B7" s="89">
-        <v>806</v>
-      </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
+      <c r="A7" s="68">
+        <v>3</v>
+      </c>
+      <c r="B7" s="70">
+        <v>788.8</v>
+      </c>
+      <c r="C7" s="101"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="84">
-        <v>3</v>
-      </c>
-      <c r="B8" s="89">
-        <v>788.8</v>
-      </c>
-      <c r="C8" s="99"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="84">
-        <v>4</v>
-      </c>
-      <c r="B9" s="89">
-        <v>788.8</v>
-      </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="84">
-        <v>5</v>
-      </c>
-      <c r="B10" s="89">
-        <v>610.4</v>
-      </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="98" t="s">
+      <c r="A8" s="74" t="s">
         <v>828</v>
       </c>
-      <c r="B11" s="89">
-        <f>SUM(B6:B10)</f>
-        <v>3746.48</v>
-      </c>
-      <c r="C11" s="99"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
+      <c r="B8" s="70">
+        <f>SUM(B6:B7)</f>
+        <v>1594.8</v>
+      </c>
+      <c r="C8" s="101"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C5:F11"/>
+    <mergeCell ref="C5:F8"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -21505,144 +21482,144 @@
       <c r="G1" s="77"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
       <c r="B2" s="102" t="s">
         <v>816</v>
       </c>
       <c r="C2" s="103"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="82" t="s">
+      <c r="D2" s="104"/>
+      <c r="E2" s="66" t="s">
         <v>758</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="67" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84">
+      <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="105" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="105"/>
+      <c r="C3" s="106"/>
       <c r="D3" s="107"/>
-      <c r="E3" s="88" t="s">
+      <c r="E3" s="69" t="s">
         <v>829</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="89">
+      <c r="G3" s="70">
         <f>B11</f>
         <v>3746.48</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="68" t="s">
         <v>831</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="84">
+      <c r="A6" s="68">
         <v>1</v>
       </c>
-      <c r="B6" s="89">
+      <c r="B6" s="70">
         <v>752.48</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="84">
+      <c r="A7" s="68">
         <v>2</v>
       </c>
-      <c r="B7" s="89">
+      <c r="B7" s="70">
         <v>806</v>
       </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="84">
+      <c r="A8" s="68">
         <v>3</v>
       </c>
-      <c r="B8" s="89">
+      <c r="B8" s="70">
         <v>788.8</v>
       </c>
-      <c r="C8" s="99"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="84">
+      <c r="A9" s="68">
         <v>4</v>
       </c>
-      <c r="B9" s="89">
+      <c r="B9" s="70">
         <v>788.8</v>
       </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="84">
+      <c r="A10" s="68">
         <v>5</v>
       </c>
-      <c r="B10" s="89">
+      <c r="B10" s="70">
         <v>610.4</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="74" t="s">
         <v>828</v>
       </c>
-      <c r="B11" s="89">
+      <c r="B11" s="70">
         <f>SUM(B6:B10)</f>
         <v>3746.48</v>
       </c>
-      <c r="C11" s="99"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -21701,7 +21678,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -21791,7 +21768,7 @@
         <v>138.798</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="42">
         <v>4</v>
       </c>
@@ -21928,7 +21905,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -22062,7 +22039,7 @@
         <v>301.05599999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="42">
         <v>6</v>
       </c>
@@ -22089,7 +22066,7 @@
         <v>31.234000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>7</v>
       </c>
@@ -22368,7 +22345,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -22428,7 +22405,7 @@
         <v>82.644000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="90" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A5" s="42">
         <v>4</v>
       </c>

--- a/hospital/стены/hospital-walls.xlsx
+++ b/hospital/стены/hospital-walls.xlsx
@@ -2,32 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" firstSheet="7" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="черновик 1-5" sheetId="16" r:id="rId1"/>
-    <sheet name="общий" sheetId="1" r:id="rId2"/>
-    <sheet name="4.1шп" sheetId="15" r:id="rId3"/>
-    <sheet name="3.1шт" sheetId="14" r:id="rId4"/>
-    <sheet name="№1" sheetId="12" r:id="rId5"/>
-    <sheet name="№2" sheetId="13" r:id="rId6"/>
-    <sheet name="1.1.1" sheetId="9" r:id="rId7"/>
-    <sheet name="1.2.1" sheetId="2" r:id="rId8"/>
-    <sheet name="1.2.2" sheetId="3" r:id="rId9"/>
-    <sheet name="1.3.1" sheetId="4" r:id="rId10"/>
-    <sheet name="1.3.2" sheetId="7" r:id="rId11"/>
-    <sheet name="1.4.1" sheetId="6" r:id="rId12"/>
-    <sheet name="1.4.2" sheetId="10" r:id="rId13"/>
-    <sheet name="1.5.1" sheetId="8" r:id="rId14"/>
+    <sheet name="2.6шт" sheetId="20" r:id="rId1"/>
+    <sheet name="2.5шт" sheetId="19" r:id="rId2"/>
+    <sheet name="Общ" sheetId="18" r:id="rId3"/>
+    <sheet name="2.4ГВЛ" sheetId="17" r:id="rId4"/>
+    <sheet name="черновик 1-5" sheetId="16" r:id="rId5"/>
+    <sheet name="общий" sheetId="1" r:id="rId6"/>
+    <sheet name="4.1шпИнв" sheetId="15" r:id="rId7"/>
+    <sheet name="3.3ГВЛинв" sheetId="22" r:id="rId8"/>
+    <sheet name="3.2штИнв" sheetId="21" r:id="rId9"/>
+    <sheet name="3.1штИнв" sheetId="14" r:id="rId10"/>
+    <sheet name="№1" sheetId="12" r:id="rId11"/>
+    <sheet name="№2" sheetId="13" r:id="rId12"/>
+    <sheet name="1.1.1" sheetId="9" r:id="rId13"/>
+    <sheet name="1.2.1" sheetId="2" r:id="rId14"/>
+    <sheet name="1.2.2" sheetId="3" r:id="rId15"/>
+    <sheet name="1.3.1" sheetId="4" r:id="rId16"/>
+    <sheet name="1.3.2" sheetId="7" r:id="rId17"/>
+    <sheet name="1.4.1" sheetId="6" r:id="rId18"/>
+    <sheet name="1.4.2" sheetId="10" r:id="rId19"/>
+    <sheet name="1.5.1" sheetId="8" r:id="rId20"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="928">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -2538,6 +2544,285 @@
   <si>
     <t>2, 3 этаж
 базовая шпаклевка</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>504а</t>
+  </si>
+  <si>
+    <t>504б</t>
+  </si>
+  <si>
+    <t>507а</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>449а</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>№ помещения</t>
+  </si>
+  <si>
+    <t>1 тип: высококачественная цементно-песчаная по сетке, м²</t>
+  </si>
+  <si>
+    <t>2 тип: улучшенная по пластиковой сетке до 10 мм, м²</t>
+  </si>
+  <si>
+    <t>3 тип: под плитку / HPL (без описания), м²</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>`-1 этаж</t>
+  </si>
+  <si>
+    <t>Подвал</t>
   </si>
 </sst>
 </file>
@@ -2999,7 +3284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3215,7 +3500,73 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3236,38 +3587,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3281,26 +3608,29 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3308,7 +3638,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3616,39 +3946,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="92" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="93" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="66" t="s">
+      <c r="C2" s="94"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="83" t="s">
         <v>758</v>
       </c>
       <c r="F2" s="67" t="s">
@@ -3658,289 +3988,82 @@
         <v>817</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68">
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="82">
         <v>1</v>
       </c>
-      <c r="B3" s="81" t="s">
-        <v>516</v>
-      </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="69" t="s">
-        <v>830</v>
-      </c>
-      <c r="F3" s="68" t="s">
+      <c r="B3" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="84" t="s">
+        <v>926</v>
+      </c>
+      <c r="F3" s="82" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="70">
-        <f>C12</f>
-        <v>4102.8599999999997</v>
+        <f>B7</f>
+        <v>375.2</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85" t="s">
-        <v>818</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="82" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
-        <v>819</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>820</v>
-      </c>
-      <c r="C6" s="68" t="s">
-        <v>821</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>822</v>
-      </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
+      <c r="A6" s="82">
+        <v>-1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>375.2</v>
+      </c>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="68">
-        <v>1</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>823</v>
-      </c>
-      <c r="C7" s="71">
-        <f>D7*3.8</f>
-        <v>866.4</v>
-      </c>
-      <c r="D7" s="71">
-        <v>228</v>
-      </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="68">
-        <v>2</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>824</v>
-      </c>
-      <c r="C8" s="71">
-        <f>D8*3.8</f>
-        <v>938.9799999999999</v>
-      </c>
-      <c r="D8" s="71">
-        <v>247.1</v>
-      </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="68">
-        <v>3</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>825</v>
-      </c>
-      <c r="C9" s="71">
-        <f>D9*3.8</f>
-        <v>925.68</v>
-      </c>
-      <c r="D9" s="71">
-        <v>243.6</v>
-      </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="68">
-        <v>4</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>826</v>
-      </c>
-      <c r="C10" s="71">
-        <f>D10*3.8</f>
-        <v>925.68</v>
-      </c>
-      <c r="D10" s="71">
-        <v>243.6</v>
-      </c>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="68">
-        <v>5</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>827</v>
-      </c>
-      <c r="C11" s="71">
-        <f>D11*3.8</f>
-        <v>446.12</v>
-      </c>
-      <c r="D11" s="71">
-        <v>117.4</v>
-      </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="s">
+      <c r="A7" s="85" t="s">
         <v>828</v>
       </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="73">
-        <f>SUM(C7:C11)</f>
-        <v>4102.8599999999997</v>
-      </c>
-      <c r="D12" s="73">
-        <v>1200</v>
-      </c>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-    </row>
-    <row r="17" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I17" t="s">
-        <v>833</v>
-      </c>
-      <c r="J17" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I18">
-        <v>227.32</v>
-      </c>
-      <c r="J18">
-        <f>I18*4</f>
-        <v>909.28</v>
-      </c>
-      <c r="L18">
-        <v>49</v>
-      </c>
-      <c r="M18">
-        <f>L18*1.6*2</f>
-        <v>156.80000000000001</v>
-      </c>
-      <c r="N18">
-        <f>J18-M18</f>
-        <v>752.48</v>
-      </c>
-    </row>
-    <row r="19" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I19">
-        <v>247.1</v>
-      </c>
-      <c r="J19">
-        <f>I19*4</f>
-        <v>988.4</v>
-      </c>
-      <c r="L19">
-        <v>57</v>
-      </c>
-      <c r="M19">
-        <f>L19*1.6*2</f>
-        <v>182.4</v>
-      </c>
-      <c r="N19">
-        <f>J19-M19</f>
-        <v>806</v>
-      </c>
-    </row>
-    <row r="20" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I20">
-        <v>243.6</v>
-      </c>
-      <c r="J20">
-        <f>I20*4</f>
-        <v>974.4</v>
-      </c>
-      <c r="L20">
-        <v>58</v>
-      </c>
-      <c r="M20">
-        <f>L20*1.6*2</f>
-        <v>185.60000000000002</v>
-      </c>
-      <c r="N20">
-        <f>J20-M20</f>
-        <v>788.8</v>
-      </c>
-    </row>
-    <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21">
-        <v>243.6</v>
-      </c>
-      <c r="J21">
-        <f>I21*4</f>
-        <v>974.4</v>
-      </c>
-      <c r="L21">
-        <v>58</v>
-      </c>
-      <c r="M21">
-        <f>L21*1.6*2</f>
-        <v>185.60000000000002</v>
-      </c>
-      <c r="N21">
-        <f>J21-M21</f>
-        <v>788.8</v>
-      </c>
-    </row>
-    <row r="22" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I22">
-        <v>177.4</v>
-      </c>
-      <c r="J22">
-        <f>I22*4</f>
-        <v>709.6</v>
-      </c>
-      <c r="L22">
-        <v>31</v>
-      </c>
-      <c r="M22">
-        <f>L22*1.6*2</f>
-        <v>99.2</v>
-      </c>
-      <c r="N22">
-        <f>J22-M22</f>
-        <v>610.4</v>
-      </c>
+      <c r="B7" s="70">
+        <f>SUM(B6:B6)</f>
+        <v>375.2</v>
+      </c>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G12"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C5:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3948,7 +4071,1544 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr codeName="Лист6"/>
+  <dimension ref="A1:L72"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="93" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="94"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="66" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="68">
+        <v>1</v>
+      </c>
+      <c r="B3" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="69" t="s">
+        <v>829</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B11</f>
+        <v>3746.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="68" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="68">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>752.48</v>
+      </c>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="68">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>806</v>
+      </c>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="68">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>788.8</v>
+      </c>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="68">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>788.8</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="68">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70">
+        <v>610.4</v>
+      </c>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="74" t="s">
+        <v>828</v>
+      </c>
+      <c r="B11" s="70">
+        <f>SUM(B6:B10)</f>
+        <v>3746.48</v>
+      </c>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H15" s="77">
+        <v>1</v>
+      </c>
+      <c r="I15" s="77">
+        <v>2</v>
+      </c>
+      <c r="J15" s="77">
+        <v>3</v>
+      </c>
+      <c r="K15" s="77">
+        <v>4</v>
+      </c>
+      <c r="L15" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="77">
+        <v>11.7</v>
+      </c>
+      <c r="I16" s="77">
+        <v>86.7</v>
+      </c>
+      <c r="J16" s="77">
+        <v>170.3</v>
+      </c>
+      <c r="K16" s="77">
+        <v>174.1</v>
+      </c>
+      <c r="L16" s="77">
+        <v>728.2</v>
+      </c>
+    </row>
+    <row r="17" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H17" s="77">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="I17" s="77">
+        <v>481.4</v>
+      </c>
+      <c r="J17" s="77">
+        <v>397.6</v>
+      </c>
+      <c r="K17" s="77">
+        <v>407.6</v>
+      </c>
+      <c r="L17" s="77">
+        <v>198.1</v>
+      </c>
+    </row>
+    <row r="18" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H18" s="77">
+        <v>279.7</v>
+      </c>
+      <c r="I18" s="77">
+        <v>286</v>
+      </c>
+      <c r="J18" s="77">
+        <v>277</v>
+      </c>
+      <c r="K18" s="77">
+        <v>366.9</v>
+      </c>
+      <c r="L18" s="77">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="19" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H19" s="77">
+        <v>456</v>
+      </c>
+      <c r="I19" s="77">
+        <v>57.3</v>
+      </c>
+      <c r="J19" s="77">
+        <v>60.5</v>
+      </c>
+      <c r="K19" s="77">
+        <v>43.2</v>
+      </c>
+      <c r="L19" s="77">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="20" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H20" s="77">
+        <v>76.5</v>
+      </c>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77">
+        <v>13.6</v>
+      </c>
+      <c r="L20" s="77"/>
+    </row>
+    <row r="21" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+    </row>
+    <row r="22" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+    </row>
+    <row r="23" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+    </row>
+    <row r="24" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="77"/>
+    </row>
+    <row r="25" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77"/>
+    </row>
+    <row r="26" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="77"/>
+      <c r="K26" s="77"/>
+      <c r="L26" s="77"/>
+    </row>
+    <row r="27" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="77"/>
+    </row>
+    <row r="28" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="77"/>
+    </row>
+    <row r="29" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+    </row>
+    <row r="30" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77"/>
+    </row>
+    <row r="31" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77"/>
+    </row>
+    <row r="32" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+    </row>
+    <row r="33" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+    </row>
+    <row r="34" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+    </row>
+    <row r="35" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="77"/>
+    </row>
+    <row r="36" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="77"/>
+    </row>
+    <row r="37" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="77"/>
+    </row>
+    <row r="38" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="77"/>
+    </row>
+    <row r="39" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+    </row>
+    <row r="40" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+    </row>
+    <row r="41" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+    </row>
+    <row r="42" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="77"/>
+    </row>
+    <row r="43" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="77"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="77"/>
+    </row>
+    <row r="44" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="77"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="77"/>
+    </row>
+    <row r="45" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H45" s="77"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="77"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+    </row>
+    <row r="46" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H46" s="77"/>
+      <c r="I46" s="77"/>
+      <c r="J46" s="77"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="77"/>
+    </row>
+    <row r="47" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="77"/>
+    </row>
+    <row r="48" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H48" s="77"/>
+      <c r="I48" s="77"/>
+      <c r="J48" s="77"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="77"/>
+    </row>
+    <row r="49" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H49" s="77"/>
+      <c r="I49" s="77"/>
+      <c r="J49" s="77"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="77"/>
+    </row>
+    <row r="50" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="77"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="77"/>
+    </row>
+    <row r="51" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H51" s="77"/>
+      <c r="I51" s="77"/>
+      <c r="J51" s="77"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="77"/>
+    </row>
+    <row r="52" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H52" s="77"/>
+      <c r="I52" s="77"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="77"/>
+    </row>
+    <row r="53" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H53" s="77"/>
+      <c r="I53" s="77"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="77"/>
+      <c r="L53" s="77"/>
+    </row>
+    <row r="54" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H54" s="77"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="77"/>
+      <c r="L54" s="77"/>
+    </row>
+    <row r="55" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H55" s="77"/>
+      <c r="I55" s="77"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="77"/>
+      <c r="L55" s="77"/>
+    </row>
+    <row r="56" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="77"/>
+    </row>
+    <row r="57" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H57" s="77"/>
+      <c r="I57" s="77"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="77"/>
+      <c r="L57" s="77"/>
+    </row>
+    <row r="58" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H58" s="77"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+    </row>
+    <row r="59" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H59" s="77"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+    </row>
+    <row r="60" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H60" s="77"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="77"/>
+      <c r="L60" s="77"/>
+    </row>
+    <row r="61" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+    </row>
+    <row r="62" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H62" s="77"/>
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="77"/>
+    </row>
+    <row r="63" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H63" s="77"/>
+      <c r="I63" s="77"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="77"/>
+    </row>
+    <row r="64" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H64" s="77"/>
+      <c r="I64" s="77"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="77"/>
+      <c r="L64" s="77"/>
+    </row>
+    <row r="65" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="77"/>
+      <c r="K65" s="77"/>
+      <c r="L65" s="77"/>
+    </row>
+    <row r="66" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="77"/>
+      <c r="K66" s="77"/>
+      <c r="L66" s="77"/>
+    </row>
+    <row r="67" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H67" s="77"/>
+      <c r="I67" s="77"/>
+      <c r="J67" s="77"/>
+      <c r="K67" s="77"/>
+      <c r="L67" s="77"/>
+    </row>
+    <row r="68" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H68" s="77"/>
+      <c r="I68" s="77"/>
+      <c r="J68" s="77"/>
+      <c r="K68" s="77"/>
+      <c r="L68" s="77"/>
+    </row>
+    <row r="69" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H69" s="77"/>
+      <c r="I69" s="77"/>
+      <c r="J69" s="77"/>
+      <c r="K69" s="77"/>
+      <c r="L69" s="77"/>
+    </row>
+    <row r="70" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H70" s="77"/>
+      <c r="I70" s="77"/>
+      <c r="J70" s="77"/>
+      <c r="K70" s="77"/>
+      <c r="L70" s="77"/>
+    </row>
+    <row r="71" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H71" s="77"/>
+      <c r="I71" s="77"/>
+      <c r="J71" s="77"/>
+      <c r="K71" s="77"/>
+      <c r="L71" s="77"/>
+    </row>
+    <row r="72" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H72" s="77"/>
+      <c r="I72" s="77"/>
+      <c r="J72" s="77"/>
+      <c r="K72" s="77"/>
+      <c r="L72" s="77"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C5:G11"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист7">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="9" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>763</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>764</v>
+      </c>
+      <c r="I1" s="60" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f>SUM(G2:I2)</f>
+        <v>4460.3999999999996</v>
+      </c>
+      <c r="G2" s="59">
+        <v>1454</v>
+      </c>
+      <c r="H2" s="59">
+        <v>1542.5</v>
+      </c>
+      <c r="I2" s="59">
+        <v>1463.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <f>SUM(G3:I3)</f>
+        <v>134.09899999999999</v>
+      </c>
+      <c r="G3" s="8">
+        <v>44.883999999999993</v>
+      </c>
+      <c r="H3" s="8">
+        <v>44.134999999999998</v>
+      </c>
+      <c r="I3" s="8">
+        <v>45.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F7" si="0">SUM(G4:J4)</f>
+        <v>322.42200000000003</v>
+      </c>
+      <c r="G4" s="8">
+        <v>82.644000000000005</v>
+      </c>
+      <c r="H4" s="8">
+        <v>100.98</v>
+      </c>
+      <c r="I4" s="8">
+        <v>138.798</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="0"/>
+        <v>56.38900000000001</v>
+      </c>
+      <c r="G5" s="8">
+        <v>17.622</v>
+      </c>
+      <c r="H5" s="8">
+        <v>15.778000000000002</v>
+      </c>
+      <c r="I5" s="8">
+        <v>22.989000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="0"/>
+        <v>118.31900000000002</v>
+      </c>
+      <c r="G6" s="8">
+        <v>45.936</v>
+      </c>
+      <c r="H6" s="8">
+        <v>47.138000000000005</v>
+      </c>
+      <c r="I6" s="8">
+        <v>25.245000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="0"/>
+        <v>1530.683</v>
+      </c>
+      <c r="G7" s="8">
+        <v>514.899</v>
+      </c>
+      <c r="H7" s="8">
+        <v>515.59199999999998</v>
+      </c>
+      <c r="I7" s="8">
+        <v>500.19199999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист8">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="8" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>813</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f>SUM(G2:H2)</f>
+        <v>2106.4780000000001</v>
+      </c>
+      <c r="G2" s="59">
+        <v>1342</v>
+      </c>
+      <c r="H2" s="59">
+        <v>764.47800000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>24.849</v>
+      </c>
+      <c r="G3" s="59">
+        <v>0</v>
+      </c>
+      <c r="H3" s="59">
+        <v>24.849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="59">
+        <f t="shared" ref="F4:F9" si="0">SUM(G4:H4)</f>
+        <v>247.184</v>
+      </c>
+      <c r="G4" s="8">
+        <v>186.2</v>
+      </c>
+      <c r="H4" s="8">
+        <v>60.984000000000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="59">
+        <f t="shared" si="0"/>
+        <v>56.835999999999999</v>
+      </c>
+      <c r="G5" s="8">
+        <v>48.8</v>
+      </c>
+      <c r="H5" s="8">
+        <v>8.0359999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="59">
+        <f>SUM(G6:H6)</f>
+        <v>826.25600000000009</v>
+      </c>
+      <c r="G6" s="8">
+        <v>525.20000000000005</v>
+      </c>
+      <c r="H6" s="8">
+        <v>301.05599999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="59">
+        <f>SUM(G7:H7)</f>
+        <v>49.534000000000006</v>
+      </c>
+      <c r="G7" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="H7" s="8">
+        <v>31.234000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="59">
+        <f t="shared" si="0"/>
+        <v>58.639000000000003</v>
+      </c>
+      <c r="G8" s="8">
+        <v>21.1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>37.539000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="42">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="59">
+        <f t="shared" si="0"/>
+        <v>28.867000000000004</v>
+      </c>
+      <c r="G9" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H9" s="8">
+        <v>10.767000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист9">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="44.88671875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="61.88671875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>186.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>525.20000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист10">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>44.883999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>82.644000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>17.622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>45.936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>514.899</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист11"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8">
+        <v>21.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист12">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
@@ -4109,8 +5769,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист13"/>
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4169,9 +5830,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr codeName="Лист14">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
@@ -4332,8 +5993,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист15"/>
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4392,9 +6054,187 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr codeName="Лист17"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="93" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="94"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="79" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78">
+        <v>1</v>
+      </c>
+      <c r="B3" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="80" t="s">
+        <v>829</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>B11</f>
+        <v>4716.6000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="78" t="s">
+        <v>831</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="78">
+        <v>1</v>
+      </c>
+      <c r="B6" s="70">
+        <v>905.8</v>
+      </c>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="78">
+        <v>2</v>
+      </c>
+      <c r="B7" s="70">
+        <v>911.4</v>
+      </c>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="78">
+        <v>3</v>
+      </c>
+      <c r="B8" s="70">
+        <v>905.40000000000009</v>
+      </c>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="78">
+        <v>4</v>
+      </c>
+      <c r="B9" s="70">
+        <v>1005.4000000000001</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="78">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70">
+        <v>988.60000000000014</v>
+      </c>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="81" t="s">
+        <v>828</v>
+      </c>
+      <c r="B11" s="70">
+        <f>SUM(B6:B10)</f>
+        <v>4716.6000000000004</v>
+      </c>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист16">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
@@ -4595,8 +6435,1806 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист1">
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:L90"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="88"/>
+    <col min="2" max="4" width="13.88671875" style="77" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="87" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="86" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="87" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1" s="87" t="s">
+        <v>896</v>
+      </c>
+      <c r="D1" s="87" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="88" t="s">
+        <v>854</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C2" s="77">
+        <v>54.2</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="88" t="s">
+        <v>855</v>
+      </c>
+      <c r="B3" s="77">
+        <v>45.03</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G3" s="77">
+        <v>0</v>
+      </c>
+      <c r="H3" s="77">
+        <v>1</v>
+      </c>
+      <c r="I3" s="77">
+        <v>2</v>
+      </c>
+      <c r="J3" s="77">
+        <v>3</v>
+      </c>
+      <c r="K3" s="77">
+        <v>4</v>
+      </c>
+      <c r="L3" s="77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="88" t="s">
+        <v>856</v>
+      </c>
+      <c r="B4" s="77">
+        <v>278.32</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G4" s="77">
+        <v>1749</v>
+      </c>
+      <c r="H4" s="77">
+        <v>11.7</v>
+      </c>
+      <c r="I4" s="77">
+        <v>86.7</v>
+      </c>
+      <c r="J4" s="77">
+        <v>170.3</v>
+      </c>
+      <c r="K4" s="77">
+        <v>174.1</v>
+      </c>
+      <c r="L4" s="77">
+        <v>728.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>857</v>
+      </c>
+      <c r="B5" s="77">
+        <v>29.72</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="G5" s="77">
+        <v>254.2</v>
+      </c>
+      <c r="H5" s="77">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="I5" s="77">
+        <v>481.4</v>
+      </c>
+      <c r="J5" s="77">
+        <v>397.6</v>
+      </c>
+      <c r="K5" s="77">
+        <v>407.6</v>
+      </c>
+      <c r="L5" s="77">
+        <v>198.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
+        <v>839</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D6" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="G6" s="77">
+        <v>910.3</v>
+      </c>
+      <c r="H6" s="77">
+        <v>279.7</v>
+      </c>
+      <c r="I6" s="77">
+        <v>286</v>
+      </c>
+      <c r="J6" s="77">
+        <v>277</v>
+      </c>
+      <c r="K6" s="77">
+        <v>366.9</v>
+      </c>
+      <c r="L6" s="77">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D7" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="G7" s="77">
+        <v>11.2</v>
+      </c>
+      <c r="H7" s="77">
+        <v>456</v>
+      </c>
+      <c r="I7" s="77">
+        <v>57.3</v>
+      </c>
+      <c r="J7" s="77">
+        <v>60.5</v>
+      </c>
+      <c r="K7" s="77">
+        <v>43.2</v>
+      </c>
+      <c r="L7" s="77">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
+        <v>859</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D8" s="77">
+        <v>144.29</v>
+      </c>
+      <c r="H8" s="77">
+        <v>76.5</v>
+      </c>
+      <c r="K8" s="77">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="88" t="s">
+        <v>860</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D9" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="88" t="s">
+        <v>861</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D10" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="88" t="s">
+        <v>862</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D11" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="88" t="s">
+        <v>863</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D12" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="88" t="s">
+        <v>864</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D13" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="88" t="s">
+        <v>865</v>
+      </c>
+      <c r="B14" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C14" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="88" t="s">
+        <v>840</v>
+      </c>
+      <c r="B15" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D15" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="88" t="s">
+        <v>866</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D16" s="77">
+        <v>17.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="88" t="s">
+        <v>867</v>
+      </c>
+      <c r="B17" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="88" t="s">
+        <v>868</v>
+      </c>
+      <c r="B18" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D18" s="77">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="88" t="s">
+        <v>869</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D19" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
+        <v>870</v>
+      </c>
+      <c r="B20" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D20" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88" t="s">
+        <v>841</v>
+      </c>
+      <c r="B21" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D21" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88" t="s">
+        <v>842</v>
+      </c>
+      <c r="B22" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C22" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D22" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88" t="s">
+        <v>843</v>
+      </c>
+      <c r="B23" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D23" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88" t="s">
+        <v>871</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D24" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
+        <v>872</v>
+      </c>
+      <c r="B25" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C25" s="77">
+        <v>54.2</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="B26" s="77">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="C26" s="77">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="D26" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88" t="s">
+        <v>874</v>
+      </c>
+      <c r="B27" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D27" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88" t="s">
+        <v>844</v>
+      </c>
+      <c r="B28" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D28" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88" t="s">
+        <v>875</v>
+      </c>
+      <c r="B29" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C29" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D29" s="77">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="88" t="s">
+        <v>876</v>
+      </c>
+      <c r="B30" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C30" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="88" t="s">
+        <v>845</v>
+      </c>
+      <c r="B31" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D31" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="88" t="s">
+        <v>877</v>
+      </c>
+      <c r="B32" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D32" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="88" t="s">
+        <v>878</v>
+      </c>
+      <c r="B33" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D33" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="88" t="s">
+        <v>879</v>
+      </c>
+      <c r="B34" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D34" s="77">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="88" t="s">
+        <v>880</v>
+      </c>
+      <c r="B35" s="77">
+        <v>278.32</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="88" t="s">
+        <v>881</v>
+      </c>
+      <c r="B36" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D36" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="88" t="s">
+        <v>846</v>
+      </c>
+      <c r="B37" s="77">
+        <v>24.96</v>
+      </c>
+      <c r="C37" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D37" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="88" t="s">
+        <v>882</v>
+      </c>
+      <c r="B38" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D38" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="88" t="s">
+        <v>847</v>
+      </c>
+      <c r="B39" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C39" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D39" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="88" t="s">
+        <v>848</v>
+      </c>
+      <c r="B40" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C40" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D40" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="88" t="s">
+        <v>849</v>
+      </c>
+      <c r="B41" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C41" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D41" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="88" t="s">
+        <v>883</v>
+      </c>
+      <c r="B42" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C42" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D42" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="88" t="s">
+        <v>884</v>
+      </c>
+      <c r="B43" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C43" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D43" s="77">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="88" t="s">
+        <v>885</v>
+      </c>
+      <c r="B44" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C44" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D44" s="77">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="88" t="s">
+        <v>886</v>
+      </c>
+      <c r="B45" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C45" s="77">
+        <v>110.62</v>
+      </c>
+      <c r="D45" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="88" t="s">
+        <v>887</v>
+      </c>
+      <c r="B46" s="77">
+        <v>45.03</v>
+      </c>
+      <c r="C46" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D46" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="88" t="s">
+        <v>888</v>
+      </c>
+      <c r="B47" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C47" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D47" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="88" t="s">
+        <v>850</v>
+      </c>
+      <c r="B48" s="77">
+        <v>5.44</v>
+      </c>
+      <c r="C48" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D48" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="88" t="s">
+        <v>889</v>
+      </c>
+      <c r="B49" s="77">
+        <v>157.04</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D49" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="88" t="s">
+        <v>851</v>
+      </c>
+      <c r="B50" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C50" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D50" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="88" t="s">
+        <v>852</v>
+      </c>
+      <c r="B51" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C51" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D51" s="77">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="88" t="s">
+        <v>890</v>
+      </c>
+      <c r="B52" s="77">
+        <v>14.17</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D52" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="88" t="s">
+        <v>853</v>
+      </c>
+      <c r="B53" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D53" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="88" t="s">
+        <v>891</v>
+      </c>
+      <c r="B54" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C54" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D54" s="77">
+        <v>253.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="88" t="s">
+        <v>892</v>
+      </c>
+      <c r="B55" s="77">
+        <v>31.06</v>
+      </c>
+      <c r="C55" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D55" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="88" t="s">
+        <v>893</v>
+      </c>
+      <c r="B56" s="77">
+        <v>44.74</v>
+      </c>
+      <c r="C56" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D56" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="88" t="s">
+        <v>898</v>
+      </c>
+      <c r="B60" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C60" s="77">
+        <v>77.23</v>
+      </c>
+      <c r="D60" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="88" t="s">
+        <v>899</v>
+      </c>
+      <c r="B61" s="77">
+        <v>24.2</v>
+      </c>
+      <c r="C61" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D61" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="88" t="s">
+        <v>900</v>
+      </c>
+      <c r="B62" s="77">
+        <v>73.42</v>
+      </c>
+      <c r="C62" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D62" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="88" t="s">
+        <v>901</v>
+      </c>
+      <c r="B63" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C63" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D63" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="88" t="s">
+        <v>836</v>
+      </c>
+      <c r="B64" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C64" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D64" s="77">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="88" t="s">
+        <v>837</v>
+      </c>
+      <c r="B65" s="77">
+        <v>234.98</v>
+      </c>
+      <c r="C65" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D65" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="88" t="s">
+        <v>902</v>
+      </c>
+      <c r="B66" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C66" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D66" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="88" t="s">
+        <v>903</v>
+      </c>
+      <c r="B67" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C67" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D67" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="88" t="s">
+        <v>904</v>
+      </c>
+      <c r="B68" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C68" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D68" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="88" t="s">
+        <v>838</v>
+      </c>
+      <c r="B69" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C69" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D69" s="77">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="88" t="s">
+        <v>905</v>
+      </c>
+      <c r="B70" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C70" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D70" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="88" t="s">
+        <v>906</v>
+      </c>
+      <c r="B71" s="77">
+        <v>7.81</v>
+      </c>
+      <c r="C71" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D71" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="88" t="s">
+        <v>907</v>
+      </c>
+      <c r="B72" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C72" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D72" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="88" t="s">
+        <v>908</v>
+      </c>
+      <c r="B73" s="77">
+        <v>91.72</v>
+      </c>
+      <c r="C73" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D73" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="88" t="s">
+        <v>909</v>
+      </c>
+      <c r="B74" s="77">
+        <v>48.37</v>
+      </c>
+      <c r="C74" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D74" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="88" t="s">
+        <v>910</v>
+      </c>
+      <c r="B75" s="77">
+        <v>29.8</v>
+      </c>
+      <c r="C75" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D75" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="88" t="s">
+        <v>911</v>
+      </c>
+      <c r="B76" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C76" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D76" s="77">
+        <v>31.04</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="88" t="s">
+        <v>912</v>
+      </c>
+      <c r="B77" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C77" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D77" s="77">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="88" t="s">
+        <v>913</v>
+      </c>
+      <c r="B78" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C78" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D78" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="88" t="s">
+        <v>914</v>
+      </c>
+      <c r="B79" s="77">
+        <v>18.579999999999998</v>
+      </c>
+      <c r="C79" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D79" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="88" t="s">
+        <v>915</v>
+      </c>
+      <c r="B80" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C80" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D80" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="88" t="s">
+        <v>916</v>
+      </c>
+      <c r="B81" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C81" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D81" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="88" t="s">
+        <v>917</v>
+      </c>
+      <c r="B82" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D82" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="88" t="s">
+        <v>918</v>
+      </c>
+      <c r="B83" s="77">
+        <v>33.92</v>
+      </c>
+      <c r="C83" s="77">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="D83" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="88" t="s">
+        <v>919</v>
+      </c>
+      <c r="B84" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C84" s="77">
+        <v>27.88</v>
+      </c>
+      <c r="D84" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="88" t="s">
+        <v>920</v>
+      </c>
+      <c r="B85" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C85" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D85" s="77">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="88" t="s">
+        <v>921</v>
+      </c>
+      <c r="B86" s="77">
+        <v>56.51</v>
+      </c>
+      <c r="C86" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D86" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="88" t="s">
+        <v>922</v>
+      </c>
+      <c r="B87" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="C87" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D87" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="88" t="s">
+        <v>923</v>
+      </c>
+      <c r="B88" s="77">
+        <v>203.07</v>
+      </c>
+      <c r="C88" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D88" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="88" t="s">
+        <v>924</v>
+      </c>
+      <c r="B89" s="77">
+        <v>203.07</v>
+      </c>
+      <c r="C89" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D89" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="88" t="s">
+        <v>925</v>
+      </c>
+      <c r="B90" s="77">
+        <v>73.42</v>
+      </c>
+      <c r="C90" s="77" t="s">
+        <v>835</v>
+      </c>
+      <c r="D90" s="77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист2">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="8" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>813</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <f t="shared" ref="F2:F4" si="0">SUM(G2:H2)</f>
+        <v>247.184</v>
+      </c>
+      <c r="G2" s="8">
+        <v>186.2</v>
+      </c>
+      <c r="H2" s="8">
+        <v>60.984000000000009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="59">
+        <f>SUM(G3:H3)</f>
+        <v>49.534000000000006</v>
+      </c>
+      <c r="G3" s="8">
+        <v>18.3</v>
+      </c>
+      <c r="H3" s="8">
+        <v>31.234000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="59">
+        <f t="shared" si="0"/>
+        <v>28.867000000000004</v>
+      </c>
+      <c r="G4" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H4" s="8">
+        <v>10.767000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист3"/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="102" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="66" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="68">
+        <v>1</v>
+      </c>
+      <c r="B3" s="105" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="106"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="69" t="s">
+        <v>830</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="70">
+        <f>C12</f>
+        <v>4102.8599999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="108" t="s">
+        <v>818</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="68" t="s">
+        <v>819</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>820</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>821</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>822</v>
+      </c>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="68">
+        <v>1</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>823</v>
+      </c>
+      <c r="C7" s="71">
+        <f>D7*3.8</f>
+        <v>866.4</v>
+      </c>
+      <c r="D7" s="71">
+        <v>228</v>
+      </c>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="68">
+        <v>2</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>824</v>
+      </c>
+      <c r="C8" s="71">
+        <f>D8*3.8</f>
+        <v>938.9799999999999</v>
+      </c>
+      <c r="D8" s="71">
+        <v>247.1</v>
+      </c>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="68">
+        <v>3</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>825</v>
+      </c>
+      <c r="C9" s="71">
+        <f>D9*3.8</f>
+        <v>925.68</v>
+      </c>
+      <c r="D9" s="71">
+        <v>243.6</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="68">
+        <v>4</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>826</v>
+      </c>
+      <c r="C10" s="71">
+        <f>D10*3.8</f>
+        <v>925.68</v>
+      </c>
+      <c r="D10" s="71">
+        <v>243.6</v>
+      </c>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="68">
+        <v>5</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>827</v>
+      </c>
+      <c r="C11" s="71">
+        <f>D11*3.8</f>
+        <v>446.12</v>
+      </c>
+      <c r="D11" s="71">
+        <v>117.4</v>
+      </c>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="109" t="s">
+        <v>828</v>
+      </c>
+      <c r="B12" s="110"/>
+      <c r="C12" s="73">
+        <f>SUM(C7:C11)</f>
+        <v>4102.8599999999997</v>
+      </c>
+      <c r="D12" s="73">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+    </row>
+    <row r="17" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>833</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <v>227.32</v>
+      </c>
+      <c r="J18">
+        <f>I18*4</f>
+        <v>909.28</v>
+      </c>
+      <c r="L18">
+        <v>49</v>
+      </c>
+      <c r="M18">
+        <f>L18*1.6*2</f>
+        <v>156.80000000000001</v>
+      </c>
+      <c r="N18">
+        <f>J18-M18</f>
+        <v>752.48</v>
+      </c>
+    </row>
+    <row r="19" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>247.1</v>
+      </c>
+      <c r="J19">
+        <f>I19*4</f>
+        <v>988.4</v>
+      </c>
+      <c r="L19">
+        <v>57</v>
+      </c>
+      <c r="M19">
+        <f>L19*1.6*2</f>
+        <v>182.4</v>
+      </c>
+      <c r="N19">
+        <f>J19-M19</f>
+        <v>806</v>
+      </c>
+    </row>
+    <row r="20" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>243.6</v>
+      </c>
+      <c r="J20">
+        <f>I20*4</f>
+        <v>974.4</v>
+      </c>
+      <c r="L20">
+        <v>58</v>
+      </c>
+      <c r="M20">
+        <f>L20*1.6*2</f>
+        <v>185.60000000000002</v>
+      </c>
+      <c r="N20">
+        <f>J20-M20</f>
+        <v>788.8</v>
+      </c>
+    </row>
+    <row r="21" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>243.6</v>
+      </c>
+      <c r="J21">
+        <f>I21*4</f>
+        <v>974.4</v>
+      </c>
+      <c r="L21">
+        <v>58</v>
+      </c>
+      <c r="M21">
+        <f>L21*1.6*2</f>
+        <v>185.60000000000002</v>
+      </c>
+      <c r="N21">
+        <f>J21-M21</f>
+        <v>788.8</v>
+      </c>
+    </row>
+    <row r="22" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <v>177.4</v>
+      </c>
+      <c r="J22">
+        <f>I22*4</f>
+        <v>709.6</v>
+      </c>
+      <c r="L22">
+        <v>31</v>
+      </c>
+      <c r="M22">
+        <f>L22*1.6*2</f>
+        <v>99.2</v>
+      </c>
+      <c r="N22">
+        <f>J22-M22</f>
+        <v>610.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G12"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист4"/>
   <dimension ref="A1:R528"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4654,61 +8292,61 @@
       <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
     </row>
     <row r="5" spans="1:18" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
@@ -4761,17 +8399,17 @@
       <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
@@ -4787,15 +8425,15 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="93" t="s">
+      <c r="C7" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -4811,15 +8449,15 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -4835,15 +8473,15 @@
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="116"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -4859,15 +8497,15 @@
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="C10" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -4883,15 +8521,15 @@
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="93" t="s">
+      <c r="C11" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -4907,15 +8545,15 @@
       <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -7953,15 +11591,15 @@
       <c r="B108" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="93" t="s">
+      <c r="C108" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="D108" s="94"/>
-      <c r="E108" s="94"/>
-      <c r="F108" s="94"/>
-      <c r="G108" s="94"/>
-      <c r="H108" s="94"/>
-      <c r="I108" s="94"/>
+      <c r="D108" s="116"/>
+      <c r="E108" s="116"/>
+      <c r="F108" s="116"/>
+      <c r="G108" s="116"/>
+      <c r="H108" s="116"/>
+      <c r="I108" s="116"/>
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
@@ -7977,15 +11615,15 @@
       <c r="B109" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C109" s="93" t="s">
+      <c r="C109" s="115" t="s">
         <v>169</v>
       </c>
-      <c r="D109" s="94"/>
-      <c r="E109" s="94"/>
-      <c r="F109" s="94"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="94"/>
-      <c r="I109" s="94"/>
+      <c r="D109" s="116"/>
+      <c r="E109" s="116"/>
+      <c r="F109" s="116"/>
+      <c r="G109" s="116"/>
+      <c r="H109" s="116"/>
+      <c r="I109" s="116"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -8001,15 +11639,15 @@
       <c r="B110" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="93" t="s">
+      <c r="C110" s="115" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="94"/>
-      <c r="E110" s="94"/>
-      <c r="F110" s="94"/>
-      <c r="G110" s="94"/>
-      <c r="H110" s="94"/>
-      <c r="I110" s="94"/>
+      <c r="D110" s="116"/>
+      <c r="E110" s="116"/>
+      <c r="F110" s="116"/>
+      <c r="G110" s="116"/>
+      <c r="H110" s="116"/>
+      <c r="I110" s="116"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
       <c r="L110" s="9"/>
@@ -8025,15 +11663,15 @@
       <c r="B111" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C111" s="93" t="s">
+      <c r="C111" s="115" t="s">
         <v>175</v>
       </c>
-      <c r="D111" s="94"/>
-      <c r="E111" s="94"/>
-      <c r="F111" s="94"/>
-      <c r="G111" s="94"/>
-      <c r="H111" s="94"/>
-      <c r="I111" s="94"/>
+      <c r="D111" s="116"/>
+      <c r="E111" s="116"/>
+      <c r="F111" s="116"/>
+      <c r="G111" s="116"/>
+      <c r="H111" s="116"/>
+      <c r="I111" s="116"/>
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
@@ -8049,15 +11687,15 @@
       <c r="B112" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C112" s="93" t="s">
+      <c r="C112" s="115" t="s">
         <v>178</v>
       </c>
-      <c r="D112" s="94"/>
-      <c r="E112" s="94"/>
-      <c r="F112" s="94"/>
-      <c r="G112" s="94"/>
-      <c r="H112" s="94"/>
-      <c r="I112" s="94"/>
+      <c r="D112" s="116"/>
+      <c r="E112" s="116"/>
+      <c r="F112" s="116"/>
+      <c r="G112" s="116"/>
+      <c r="H112" s="116"/>
+      <c r="I112" s="116"/>
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
       <c r="L112" s="9"/>
@@ -8784,15 +12422,15 @@
       <c r="B135" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C135" s="93" t="s">
+      <c r="C135" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="94"/>
-      <c r="E135" s="94"/>
-      <c r="F135" s="94"/>
-      <c r="G135" s="94"/>
-      <c r="H135" s="94"/>
-      <c r="I135" s="94"/>
+      <c r="D135" s="116"/>
+      <c r="E135" s="116"/>
+      <c r="F135" s="116"/>
+      <c r="G135" s="116"/>
+      <c r="H135" s="116"/>
+      <c r="I135" s="116"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -10319,15 +13957,15 @@
       <c r="B180" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C180" s="93" t="s">
+      <c r="C180" s="115" t="s">
         <v>285</v>
       </c>
-      <c r="D180" s="94"/>
-      <c r="E180" s="94"/>
-      <c r="F180" s="94"/>
-      <c r="G180" s="94"/>
-      <c r="H180" s="94"/>
-      <c r="I180" s="94"/>
+      <c r="D180" s="116"/>
+      <c r="E180" s="116"/>
+      <c r="F180" s="116"/>
+      <c r="G180" s="116"/>
+      <c r="H180" s="116"/>
+      <c r="I180" s="116"/>
       <c r="J180" s="9"/>
       <c r="K180" s="9"/>
       <c r="L180" s="9"/>
@@ -13680,15 +17318,15 @@
       <c r="B285" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C285" s="93" t="s">
+      <c r="C285" s="115" t="s">
         <v>433</v>
       </c>
-      <c r="D285" s="94"/>
-      <c r="E285" s="94"/>
-      <c r="F285" s="94"/>
-      <c r="G285" s="94"/>
-      <c r="H285" s="94"/>
-      <c r="I285" s="94"/>
+      <c r="D285" s="116"/>
+      <c r="E285" s="116"/>
+      <c r="F285" s="116"/>
+      <c r="G285" s="116"/>
+      <c r="H285" s="116"/>
+      <c r="I285" s="116"/>
       <c r="J285" s="9"/>
       <c r="K285" s="9"/>
       <c r="L285" s="9"/>
@@ -13704,15 +17342,15 @@
       <c r="B286" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C286" s="93" t="s">
+      <c r="C286" s="115" t="s">
         <v>436</v>
       </c>
-      <c r="D286" s="94"/>
-      <c r="E286" s="94"/>
-      <c r="F286" s="94"/>
-      <c r="G286" s="94"/>
-      <c r="H286" s="94"/>
-      <c r="I286" s="94"/>
+      <c r="D286" s="116"/>
+      <c r="E286" s="116"/>
+      <c r="F286" s="116"/>
+      <c r="G286" s="116"/>
+      <c r="H286" s="116"/>
+      <c r="I286" s="116"/>
       <c r="J286" s="9"/>
       <c r="K286" s="9"/>
       <c r="L286" s="9"/>
@@ -14049,15 +17687,15 @@
       <c r="B297" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C297" s="93" t="s">
+      <c r="C297" s="115" t="s">
         <v>455</v>
       </c>
-      <c r="D297" s="94"/>
-      <c r="E297" s="94"/>
-      <c r="F297" s="94"/>
-      <c r="G297" s="94"/>
-      <c r="H297" s="94"/>
-      <c r="I297" s="94"/>
+      <c r="D297" s="116"/>
+      <c r="E297" s="116"/>
+      <c r="F297" s="116"/>
+      <c r="G297" s="116"/>
+      <c r="H297" s="116"/>
+      <c r="I297" s="116"/>
       <c r="J297" s="9"/>
       <c r="K297" s="9"/>
       <c r="L297" s="9"/>
@@ -14927,15 +18565,15 @@
       <c r="B324" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C324" s="93" t="s">
+      <c r="C324" s="115" t="s">
         <v>498</v>
       </c>
-      <c r="D324" s="94"/>
-      <c r="E324" s="94"/>
-      <c r="F324" s="94"/>
-      <c r="G324" s="94"/>
-      <c r="H324" s="94"/>
-      <c r="I324" s="94"/>
+      <c r="D324" s="116"/>
+      <c r="E324" s="116"/>
+      <c r="F324" s="116"/>
+      <c r="G324" s="116"/>
+      <c r="H324" s="116"/>
+      <c r="I324" s="116"/>
       <c r="J324" s="9"/>
       <c r="K324" s="9"/>
       <c r="L324" s="9"/>
@@ -14951,15 +18589,15 @@
       <c r="B325" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C325" s="93" t="s">
+      <c r="C325" s="115" t="s">
         <v>501</v>
       </c>
-      <c r="D325" s="94"/>
-      <c r="E325" s="94"/>
-      <c r="F325" s="94"/>
-      <c r="G325" s="94"/>
-      <c r="H325" s="94"/>
-      <c r="I325" s="94"/>
+      <c r="D325" s="116"/>
+      <c r="E325" s="116"/>
+      <c r="F325" s="116"/>
+      <c r="G325" s="116"/>
+      <c r="H325" s="116"/>
+      <c r="I325" s="116"/>
       <c r="J325" s="9"/>
       <c r="K325" s="9"/>
       <c r="L325" s="9"/>
@@ -15489,15 +19127,15 @@
       <c r="B342" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C342" s="93" t="s">
+      <c r="C342" s="115" t="s">
         <v>525</v>
       </c>
-      <c r="D342" s="94"/>
-      <c r="E342" s="94"/>
-      <c r="F342" s="94"/>
-      <c r="G342" s="94"/>
-      <c r="H342" s="94"/>
-      <c r="I342" s="94"/>
+      <c r="D342" s="116"/>
+      <c r="E342" s="116"/>
+      <c r="F342" s="116"/>
+      <c r="G342" s="116"/>
+      <c r="H342" s="116"/>
+      <c r="I342" s="116"/>
       <c r="J342" s="9"/>
       <c r="K342" s="9"/>
       <c r="L342" s="9"/>
@@ -16309,15 +19947,15 @@
       <c r="B367" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C367" s="93" t="s">
+      <c r="C367" s="115" t="s">
         <v>559</v>
       </c>
-      <c r="D367" s="94"/>
-      <c r="E367" s="94"/>
-      <c r="F367" s="94"/>
-      <c r="G367" s="94"/>
-      <c r="H367" s="94"/>
-      <c r="I367" s="94"/>
+      <c r="D367" s="116"/>
+      <c r="E367" s="116"/>
+      <c r="F367" s="116"/>
+      <c r="G367" s="116"/>
+      <c r="H367" s="116"/>
+      <c r="I367" s="116"/>
       <c r="J367" s="9"/>
       <c r="K367" s="9"/>
       <c r="L367" s="9"/>
@@ -18821,15 +22459,15 @@
       <c r="B447" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C447" s="93" t="s">
+      <c r="C447" s="115" t="s">
         <v>664</v>
       </c>
-      <c r="D447" s="94"/>
-      <c r="E447" s="94"/>
-      <c r="F447" s="94"/>
-      <c r="G447" s="94"/>
-      <c r="H447" s="94"/>
-      <c r="I447" s="94"/>
+      <c r="D447" s="116"/>
+      <c r="E447" s="116"/>
+      <c r="F447" s="116"/>
+      <c r="G447" s="116"/>
+      <c r="H447" s="116"/>
+      <c r="I447" s="116"/>
       <c r="J447" s="9"/>
       <c r="K447" s="9"/>
       <c r="L447" s="9"/>
@@ -18917,17 +22555,17 @@
       <c r="P449" s="9"/>
     </row>
     <row r="450" spans="1:18" ht="64.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A450" s="91" t="s">
+      <c r="A450" s="119" t="s">
         <v>671</v>
       </c>
-      <c r="B450" s="92"/>
-      <c r="C450" s="92"/>
-      <c r="D450" s="92"/>
-      <c r="E450" s="92"/>
-      <c r="F450" s="92"/>
-      <c r="G450" s="92"/>
-      <c r="H450" s="92"/>
-      <c r="I450" s="92"/>
+      <c r="B450" s="120"/>
+      <c r="C450" s="120"/>
+      <c r="D450" s="120"/>
+      <c r="E450" s="120"/>
+      <c r="F450" s="120"/>
+      <c r="G450" s="120"/>
+      <c r="H450" s="120"/>
+      <c r="I450" s="120"/>
       <c r="J450" s="26"/>
       <c r="K450" s="26"/>
       <c r="L450" s="26"/>
@@ -18943,15 +22581,15 @@
       <c r="B451" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C451" s="93" t="s">
+      <c r="C451" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="94"/>
-      <c r="E451" s="94"/>
-      <c r="F451" s="94"/>
-      <c r="G451" s="94"/>
-      <c r="H451" s="94"/>
-      <c r="I451" s="94"/>
+      <c r="D451" s="116"/>
+      <c r="E451" s="116"/>
+      <c r="F451" s="116"/>
+      <c r="G451" s="116"/>
+      <c r="H451" s="116"/>
+      <c r="I451" s="116"/>
       <c r="J451" s="9"/>
       <c r="K451" s="9"/>
       <c r="L451" s="9"/>
@@ -18967,15 +22605,15 @@
       <c r="B452" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C452" s="93" t="s">
+      <c r="C452" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="D452" s="94"/>
-      <c r="E452" s="94"/>
-      <c r="F452" s="94"/>
-      <c r="G452" s="94"/>
-      <c r="H452" s="94"/>
-      <c r="I452" s="94"/>
+      <c r="D452" s="116"/>
+      <c r="E452" s="116"/>
+      <c r="F452" s="116"/>
+      <c r="G452" s="116"/>
+      <c r="H452" s="116"/>
+      <c r="I452" s="116"/>
       <c r="J452" s="9"/>
       <c r="K452" s="9"/>
       <c r="L452" s="9"/>
@@ -18991,15 +22629,15 @@
       <c r="B453" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C453" s="93" t="s">
+      <c r="C453" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="D453" s="94"/>
-      <c r="E453" s="94"/>
-      <c r="F453" s="94"/>
-      <c r="G453" s="94"/>
-      <c r="H453" s="94"/>
-      <c r="I453" s="94"/>
+      <c r="D453" s="116"/>
+      <c r="E453" s="116"/>
+      <c r="F453" s="116"/>
+      <c r="G453" s="116"/>
+      <c r="H453" s="116"/>
+      <c r="I453" s="116"/>
       <c r="J453" s="9"/>
       <c r="K453" s="9"/>
       <c r="L453" s="9"/>
@@ -19015,15 +22653,15 @@
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C454" s="93" t="s">
+      <c r="C454" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D454" s="94"/>
-      <c r="E454" s="94"/>
-      <c r="F454" s="94"/>
-      <c r="G454" s="94"/>
-      <c r="H454" s="94"/>
-      <c r="I454" s="94"/>
+      <c r="D454" s="116"/>
+      <c r="E454" s="116"/>
+      <c r="F454" s="116"/>
+      <c r="G454" s="116"/>
+      <c r="H454" s="116"/>
+      <c r="I454" s="116"/>
       <c r="J454" s="9"/>
       <c r="K454" s="9"/>
       <c r="L454" s="9"/>
@@ -19039,15 +22677,15 @@
       <c r="B455" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C455" s="93" t="s">
+      <c r="C455" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="D455" s="94"/>
-      <c r="E455" s="94"/>
-      <c r="F455" s="94"/>
-      <c r="G455" s="94"/>
-      <c r="H455" s="94"/>
-      <c r="I455" s="94"/>
+      <c r="D455" s="116"/>
+      <c r="E455" s="116"/>
+      <c r="F455" s="116"/>
+      <c r="G455" s="116"/>
+      <c r="H455" s="116"/>
+      <c r="I455" s="116"/>
       <c r="J455" s="9"/>
       <c r="K455" s="9"/>
       <c r="L455" s="9"/>
@@ -19063,15 +22701,15 @@
       <c r="B456" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C456" s="99" t="s">
+      <c r="C456" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D456" s="100"/>
-      <c r="E456" s="100"/>
-      <c r="F456" s="100"/>
-      <c r="G456" s="100"/>
-      <c r="H456" s="100"/>
-      <c r="I456" s="100"/>
+      <c r="D456" s="118"/>
+      <c r="E456" s="118"/>
+      <c r="F456" s="118"/>
+      <c r="G456" s="118"/>
+      <c r="H456" s="118"/>
+      <c r="I456" s="118"/>
       <c r="J456" s="27"/>
       <c r="K456" s="27"/>
       <c r="L456" s="27"/>
@@ -20634,15 +24272,15 @@
       <c r="B505" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="C505" s="97" t="s">
+      <c r="C505" s="113" t="s">
         <v>433</v>
       </c>
-      <c r="D505" s="98"/>
-      <c r="E505" s="98"/>
-      <c r="F505" s="98"/>
-      <c r="G505" s="98"/>
-      <c r="H505" s="98"/>
-      <c r="I505" s="98"/>
+      <c r="D505" s="114"/>
+      <c r="E505" s="114"/>
+      <c r="F505" s="114"/>
+      <c r="G505" s="114"/>
+      <c r="H505" s="114"/>
+      <c r="I505" s="114"/>
       <c r="J505" s="9"/>
       <c r="K505" s="29"/>
       <c r="L505" s="9"/>
@@ -20658,15 +24296,15 @@
       <c r="B506" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="C506" s="97" t="s">
+      <c r="C506" s="113" t="s">
         <v>436</v>
       </c>
-      <c r="D506" s="98"/>
-      <c r="E506" s="98"/>
-      <c r="F506" s="98"/>
-      <c r="G506" s="98"/>
-      <c r="H506" s="98"/>
-      <c r="I506" s="98"/>
+      <c r="D506" s="114"/>
+      <c r="E506" s="114"/>
+      <c r="F506" s="114"/>
+      <c r="G506" s="114"/>
+      <c r="H506" s="114"/>
+      <c r="I506" s="114"/>
       <c r="J506" s="9"/>
       <c r="K506" s="29"/>
       <c r="L506" s="9"/>
@@ -20828,15 +24466,15 @@
       <c r="B512" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="C512" s="97" t="s">
+      <c r="C512" s="113" t="s">
         <v>455</v>
       </c>
-      <c r="D512" s="98"/>
-      <c r="E512" s="98"/>
-      <c r="F512" s="98"/>
-      <c r="G512" s="98"/>
-      <c r="H512" s="98"/>
-      <c r="I512" s="98"/>
+      <c r="D512" s="114"/>
+      <c r="E512" s="114"/>
+      <c r="F512" s="114"/>
+      <c r="G512" s="114"/>
+      <c r="H512" s="114"/>
+      <c r="I512" s="114"/>
       <c r="J512" s="9"/>
       <c r="K512" s="29"/>
       <c r="L512" s="9"/>
@@ -20963,7 +24601,7 @@
       <c r="O516" s="9"/>
       <c r="P516" s="9"/>
     </row>
-    <row r="517" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>740</v>
       </c>
@@ -21025,7 +24663,7 @@
       <c r="O518" s="8"/>
       <c r="P518" s="9"/>
     </row>
-    <row r="519" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" ht="90" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>742</v>
       </c>
@@ -21273,35 +24911,22 @@
       <c r="E528" s="54"/>
       <c r="F528" s="54"/>
       <c r="G528" s="54"/>
-      <c r="H528" s="95"/>
-      <c r="I528" s="96"/>
-      <c r="J528" s="96"/>
-      <c r="K528" s="96"/>
-      <c r="L528" s="96"/>
-      <c r="M528" s="96"/>
-      <c r="N528" s="96"/>
-      <c r="O528" s="96"/>
+      <c r="H528" s="111"/>
+      <c r="I528" s="112"/>
+      <c r="J528" s="112"/>
+      <c r="K528" s="112"/>
+      <c r="L528" s="112"/>
+      <c r="M528" s="112"/>
+      <c r="N528" s="112"/>
+      <c r="O528" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="H528:O528"/>
-    <mergeCell ref="C505:I505"/>
-    <mergeCell ref="C506:I506"/>
-    <mergeCell ref="C512:I512"/>
-    <mergeCell ref="C455:I455"/>
-    <mergeCell ref="C456:I456"/>
-    <mergeCell ref="C454:I454"/>
-    <mergeCell ref="C286:I286"/>
-    <mergeCell ref="C297:I297"/>
-    <mergeCell ref="C324:I324"/>
-    <mergeCell ref="C325:I325"/>
-    <mergeCell ref="C342:I342"/>
-    <mergeCell ref="C367:I367"/>
-    <mergeCell ref="C447:I447"/>
-    <mergeCell ref="A450:I450"/>
-    <mergeCell ref="C451:I451"/>
-    <mergeCell ref="C452:I452"/>
-    <mergeCell ref="C453:I453"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C7:I7"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C285:I285"/>
     <mergeCell ref="C9:I9"/>
@@ -21315,19 +24940,33 @@
     <mergeCell ref="C112:I112"/>
     <mergeCell ref="C135:I135"/>
     <mergeCell ref="C180:I180"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C454:I454"/>
+    <mergeCell ref="C286:I286"/>
+    <mergeCell ref="C297:I297"/>
+    <mergeCell ref="C324:I324"/>
+    <mergeCell ref="C325:I325"/>
+    <mergeCell ref="C342:I342"/>
+    <mergeCell ref="C367:I367"/>
+    <mergeCell ref="C447:I447"/>
+    <mergeCell ref="A450:I450"/>
+    <mergeCell ref="C451:I451"/>
+    <mergeCell ref="C452:I452"/>
+    <mergeCell ref="C453:I453"/>
+    <mergeCell ref="H528:O528"/>
+    <mergeCell ref="C505:I505"/>
+    <mergeCell ref="C506:I506"/>
+    <mergeCell ref="C512:I512"/>
+    <mergeCell ref="C455:I455"/>
+    <mergeCell ref="C456:I456"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист5"/>
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -21341,23 +24980,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="92" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-    </row>
-    <row r="2" spans="1:6" s="110" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+    </row>
+    <row r="2" spans="1:6" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="76" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="123" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="109"/>
+      <c r="C2" s="124"/>
       <c r="D2" s="76" t="s">
         <v>758</v>
       </c>
@@ -21372,10 +25011,10 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="105" t="s">
         <v>832</v>
       </c>
-      <c r="C3" s="83"/>
+      <c r="C3" s="107"/>
       <c r="D3" s="75" t="s">
         <v>834</v>
       </c>
@@ -21388,12 +25027,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
@@ -21402,10 +25041,10 @@
       <c r="B5" s="68" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
@@ -21414,10 +25053,10 @@
       <c r="B6" s="70">
         <v>806</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
@@ -21426,10 +25065,10 @@
       <c r="B7" s="70">
         <v>788.8</v>
       </c>
-      <c r="C7" s="101"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="74" t="s">
@@ -21439,10 +25078,10 @@
         <f>SUM(B6:B7)</f>
         <v>1594.8</v>
       </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -21456,9 +25095,190 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="59">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="8">
+        <v>93.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="42">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8">
+        <v>262.60000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="42">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+      <c r="A7" s="42">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>10.55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -21471,26 +25291,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="92" t="s">
         <v>814</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+    </row>
+    <row r="2" spans="1:7" s="77" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="89" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="123" t="s">
         <v>816</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="66" t="s">
+      <c r="C2" s="125"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="91" t="s">
         <v>758</v>
       </c>
       <c r="F2" s="67" t="s">
@@ -21500,1033 +25320,31 @@
         <v>817</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68">
+    <row r="3" spans="1:7" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="96" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="69" t="s">
-        <v>829</v>
-      </c>
-      <c r="F3" s="68" t="s">
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="90" t="s">
+        <v>927</v>
+      </c>
+      <c r="F3" s="89" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="70">
-        <f>B11</f>
-        <v>3746.48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
-        <v>831</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>821</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="68">
-        <v>1</v>
-      </c>
-      <c r="B6" s="70">
-        <v>752.48</v>
-      </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="68">
-        <v>2</v>
-      </c>
-      <c r="B7" s="70">
-        <v>806</v>
-      </c>
-      <c r="C7" s="101"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="68">
-        <v>3</v>
-      </c>
-      <c r="B8" s="70">
-        <v>788.8</v>
-      </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="68">
-        <v>4</v>
-      </c>
-      <c r="B9" s="70">
-        <v>788.8</v>
-      </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="68">
-        <v>5</v>
-      </c>
-      <c r="B10" s="70">
-        <v>610.4</v>
-      </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="74" t="s">
-        <v>828</v>
-      </c>
-      <c r="B11" s="70">
-        <f>SUM(B6:B10)</f>
-        <v>3746.48</v>
-      </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
+        <v>2924.7</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C5:G11"/>
-    <mergeCell ref="A4:G4"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="9" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>763</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>764</v>
-      </c>
-      <c r="I1" s="60" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <f>SUM(G2:I2)</f>
-        <v>4460.3999999999996</v>
-      </c>
-      <c r="G2" s="59">
-        <v>1454</v>
-      </c>
-      <c r="H2" s="59">
-        <v>1542.5</v>
-      </c>
-      <c r="I2" s="59">
-        <v>1463.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <f>SUM(G3:I3)</f>
-        <v>134.09899999999999</v>
-      </c>
-      <c r="G3" s="8">
-        <v>44.883999999999993</v>
-      </c>
-      <c r="H3" s="8">
-        <v>44.134999999999998</v>
-      </c>
-      <c r="I3" s="8">
-        <v>45.08</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <f t="shared" ref="F4:F7" si="0">SUM(G4:J4)</f>
-        <v>322.42200000000003</v>
-      </c>
-      <c r="G4" s="8">
-        <v>82.644000000000005</v>
-      </c>
-      <c r="H4" s="8">
-        <v>100.98</v>
-      </c>
-      <c r="I4" s="8">
-        <v>138.798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" si="0"/>
-        <v>56.38900000000001</v>
-      </c>
-      <c r="G5" s="8">
-        <v>17.622</v>
-      </c>
-      <c r="H5" s="8">
-        <v>15.778000000000002</v>
-      </c>
-      <c r="I5" s="8">
-        <v>22.989000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <f t="shared" si="0"/>
-        <v>118.31900000000002</v>
-      </c>
-      <c r="G6" s="8">
-        <v>45.936</v>
-      </c>
-      <c r="H6" s="8">
-        <v>47.138000000000005</v>
-      </c>
-      <c r="I6" s="8">
-        <v>25.245000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="0"/>
-        <v>1530.683</v>
-      </c>
-      <c r="G7" s="8">
-        <v>514.899</v>
-      </c>
-      <c r="H7" s="8">
-        <v>515.59199999999998</v>
-      </c>
-      <c r="I7" s="8">
-        <v>500.19199999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="8" width="16.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>813</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="59">
-        <f>SUM(G2:H2)</f>
-        <v>2106.4780000000001</v>
-      </c>
-      <c r="G2" s="59">
-        <v>1342</v>
-      </c>
-      <c r="H2" s="59">
-        <v>764.47800000000007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>24.849</v>
-      </c>
-      <c r="G3" s="59">
-        <v>0</v>
-      </c>
-      <c r="H3" s="59">
-        <v>24.849</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="59">
-        <f t="shared" ref="F4:F9" si="0">SUM(G4:H4)</f>
-        <v>247.184</v>
-      </c>
-      <c r="G4" s="8">
-        <v>186.2</v>
-      </c>
-      <c r="H4" s="8">
-        <v>60.984000000000009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="59">
-        <f t="shared" si="0"/>
-        <v>56.835999999999999</v>
-      </c>
-      <c r="G5" s="8">
-        <v>48.8</v>
-      </c>
-      <c r="H5" s="8">
-        <v>8.0359999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="59">
-        <f>SUM(G6:H6)</f>
-        <v>826.25600000000009</v>
-      </c>
-      <c r="G6" s="8">
-        <v>525.20000000000005</v>
-      </c>
-      <c r="H6" s="8">
-        <v>301.05599999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="59">
-        <f>SUM(G7:H7)</f>
-        <v>49.534000000000006</v>
-      </c>
-      <c r="G7" s="8">
-        <v>18.3</v>
-      </c>
-      <c r="H7" s="8">
-        <v>31.234000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="59">
-        <f t="shared" si="0"/>
-        <v>58.639000000000003</v>
-      </c>
-      <c r="G8" s="8">
-        <v>21.1</v>
-      </c>
-      <c r="H8" s="8">
-        <v>37.539000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="59">
-        <f t="shared" si="0"/>
-        <v>28.867000000000004</v>
-      </c>
-      <c r="G9" s="8">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="H9" s="8">
-        <v>10.767000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.33203125" style="20" customWidth="1"/>
-    <col min="2" max="2" width="44.88671875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="61.88671875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>186.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>525.20000000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A8" s="42">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="8">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="8">
-        <v>44.883999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="8">
-        <v>82.644000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A5" s="42">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8">
-        <v>17.622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8">
-        <v>45.936</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8">
-        <v>514.899</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="20" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>757</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>758</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A2" s="42">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="8">
-        <v>21.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
 </file>